--- a/docs/triton-learning/cards/triton-lesson-02-fused-softmax-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-02-fused-softmax-technical-qa.xlsx
@@ -36,15 +36,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">softmax 的 padding 为什么填负无穷？</t>
+          <t xml:space="preserve">Triton 按行计算 softmax 时，通常把一行的有效列补到较大的块宽度。假设有效输入非空且全部有限，为什么 tl.load 对超出有效列数的位置应填负无穷，而不能随意填零？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它在 max 归约中不改变最大值，经减最大值和取指数后又变成求和单位元 0。
-• [T#B#最大值]：有效元素给出有限行最大值 m；padding 的负无穷不会改变 m。
-• [T#B#指数和]：负无穷减去有限 m 仍是负无穷；exp(负无穷)=0，不增加分母。
-[T#B,!c47f17#边界]：前提是行非空且有效输入有限；全为负无穷等非有限输入需要另定语义。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：负无穷不会改变有效元素的最大值，并且在减去行最大值、取指数后变成 0，从而既不影响 max，也不增加 softmax 的归一化分母。
+• [T#B#先求最大值]：令 m 为有效输入的行最大值。额外的负无穷位置不会超过任何有限有效值，因此整块求 max 仍得到 m；若填零，在有效值全为负数时就会改变最大值。
+• [T#B#再取指数求和]：padding 的负无穷减去有限 m 后仍为负无穷，取 exp 得 0。把它们加入指数和，对分母没有贡献；零填充则可能产生额外正贡献。
+• [T#B#最终输出]：只有有效列的位置需要写回；padding 只是为块级计算补齐形状，不是 softmax 输入中新增的有效元素。
+[T#B,!c47f17#边界]：上述推导要求有至少一个有效元素且有效输入有限。整行均为负无穷等情形可能遇到未定义运算，需要另行规定语义。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -61,14 +62,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本课 softmax 怎样处理 M=0 与 N=0？</t>
+          <t xml:space="preserve">本课的 softmax 接口接收形状 \[M, N\] 的矩阵，其中 M 是行数，N 是每行参与 softmax 的列数。为什么约定 M=0 且 N&gt;0 可返回空结果，而 N=0 要拒绝？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：M=0 且 N&gt;0 返回空结果；N=0 明确拒绝。
-• [T#B#区别]：前者没有要处理的行；后者没有有效的行内归约域。
-[T#B,!c47f17#边界]：这是 Lesson02 学习基线的接口约定，不能推广成所有框架的统一行为。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：没有输入行，与有一个空的行内归约维度，是两种接口情况。本练习允许前者，明确拒绝后者。
+• [T#B#没有行]：M=0 且 N&gt;0 表示没有需要处理的样本行，可以返回相同形状的空结果，不必执行任何行的 max 或 sum。
+• [T#B#没有列]：N=0 表示每行没有参与 softmax 的元素，行最大值与归一化分母没有本练习所要求的有效计算域，因此 wrapper 直接拒绝该输入。
+[T#B,!c47f17#边界]：这是 Triton Lesson 02 学习实现的接口约定；不能据此断言所有深度学习框架都会以同样方式处理空形状。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -85,13 +87,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">softmax 的每行和接近 1，应检查哪一端？</t>
+          <t xml:space="preserve">测试按行计算的 softmax kernel 时，假设每行非空且有效输入都为有限值，我们希望检查“每行元素之和接近 1”这一不变量。应该对输入矩阵 X 还是输出矩阵 Y 求行和，为什么？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：检查输出每行之和接近 1；输入行和没有这项要求。
-[T#B,!c47f17#边界]：浮点计算用合理容差；该不变量检查不能单独替代 reference 对照。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：应检查输出 Y 的每行之和接近 1。softmax 把一行输入变成归一化权重，约束属于归一化后的输出，而不属于原始输入。
+• [T#B#输入没有此约束]：输入可以是任意有限分数。例如输入行 \[2, 3\] 的和为 5，并不影响它成为合法的 softmax 输入。
+• [T#B#输出为何归一化]：每个输出都是该位置的指数值除以整行指数和。将所有输出相加，分子合起来就是同一个分母，所以数学上的结果为 1。
+[T#B,!c47f17#边界]：浮点结果按合理容差比较。仅通过行和检查仍不足以证明每个输出正确，还应与可靠 reference 逐元素对照。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -108,14 +112,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">本课 num_stages 描述哪一层流水？</t>
+          <t xml:space="preserve">Triton persistent softmax 中，一个 program 会在行循环里依次处理多行。该循环 tl.range(..., num_stages=s) 的 num_stages 描述什么流水范围，能把 s 理解成 s 个独立 worker 吗？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：描述同一 program 内多个循环迭代在途、重叠的机会，实际流水由编译器安排。
-• [T#B#依赖]：同一行的 load、max、exp、sum、归一化和 store 仍有依赖。
-[T#B,!c47f17#边界]：stage 不是独立 worker，也不自动把一行切成多个并行块。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。这里 num_stages 为同一个 program 内不同循环迭代的在途与重叠提供机会，实际如何调度由编译器决定。
+• [T#B#迭代是什么]：一次迭代计算一行 softmax。存在多次迭代时，编译器可以尝试让不同迭代中可独立推进的工作重叠。
+• [T#B#依赖仍存在]：对于同一行，加载后才能求最大值，再计算指数、指数和、归一化和写回。这些依赖不会因为 num_stages 变大而消失。
+[T#B,!c47f17#边界]：stage 不是独立 program 或 worker，也不表示把一行机械切成 s 段并行处理；这里讨论的特定作用域是行循环的跨迭代流水。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -132,14 +137,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">增加流水资源压力，会先怎样限制驻留？</t>
+          <t xml:space="preserve">对同一个 GPU kernel，增加软件流水深度后，若编译结果显示每个 program 使用更多寄存器或共享内存，这种资源变化为什么可能减少每个 SM 的并行驻留数量？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 program 的资源占用增加，可能使每个 SM 可同时驻留的 programs 变少。
-• [T#B#因果]：在固定 SM 资源容量下，单 program 占用更高，会收紧资源允许的驻留上限。
-[T#B,!c47f17#边界]：不能由此断言单 stage 变慢；资源是否增长、哪种资源受限和 spilling 都需要对应证据。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 SM 的资源总量有限；一个 program 占用更多受限资源时，SM 能同时容纳的 program 数可能减少。
+• [T#B#驻留的含义]：驻留是 program 的执行状态与资源已经放在该 SM 上，能够等待或参与调度；它描述的是同时容纳多少份工作。
+• [T#B#容量如何受限]：可以把每个 program 需要的寄存器、共享内存等分别与 SM 的容量比较；其中最紧的约束会限制可同时驻留的数量。
+• [T#B#不能直接推出什么]：并行驻留数降低，并不等价于某一次 stage 本身执行更慢。若要说单个 program 因 spilling 等原因变慢，还需要该机制的证据。
+[T#B,!c47f17#边界]：增加 stages 不保证寄存器和共享内存都增长，也不保证正好保存同样数量的完整行；应检查实际编译特化的资源记录。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -156,15 +163,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">怎样证明静态 grid-stride 不漏行、不重行？</t>
+          <t xml:space="preserve">persistent softmax 有 M 行输入，启动 P 个 program（P&gt;0）。编号 p 的 program 从行 p 开始，每次增加 P，直到行号达到 M。怎样证明这种 grid-stride 分配让每一行恰好被处理一次？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个合法行号都能唯一分解为 program 编号与迭代编号。
-[E##r=p+kP,\qquad p=r\bmod P,\quad k=\lfloor r/P\rfloor]
-• [T#B#覆盖与唯一]：program p 处理 p、p+P、p+2P……；商 k 与余数 p 唯一，因此每行恰好归属一次。
-[T#B,!c47f17#边界]：P&gt;0，0≤r&lt;M，0≤p&lt;P；循环只处理 r&lt;M 的行。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：对任意合法行号，除以 P 得到唯一的商和余数；余数确定负责它的 program，商确定该 program 的循环迭代，所以既不会漏行，也不会重行。
+• [T#B#符号定义]：设 r 是行号，满足 0≤r&lt;M；p 是 program 编号，满足 0≤p&lt;P；k 是从 0 开始的迭代编号。它们满足以下对应关系。
+[E##r=p+kP,\qquad p=r\bmod P,\qquad k=\lfloor r/P\rfloor]
+• [T#B#不漏与不重]：存在这组商和余数，说明每个 r 都有对应的 program 和迭代；商余数唯一，说明不会有另一组 program 与迭代再次处理同一行。
+[T#B,!c47f17#边界]：循环必须以 r&lt;M 为条件，并使用同一个正步长 P。证明依赖这套静态行分配规则，而不是仅凭某个数字例子看起来覆盖完整。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -181,14 +189,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">本课 grid=M 时，为什么没有跨行循环流水？</t>
+          <t xml:space="preserve">persistent softmax 共有 M 行，program p 依次处理 p、p+P、p+2P 等行，其中 P 是启动的 program 数。如果实际启动 P=M，为什么增加行循环的 num_stages 不能产生同一 program 的跨行流水？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 program 只处理一行，没有自己的下一次行迭代可重叠。
-• [T#B#推导]：行分配步长为 P=M；处理行 p 后，下一个行号 p+M 已超出范围。
-[T#B,!c47f17#边界]：不同 programs 之间的交错属于硬件调度，不属于该 program 内 tl.range 的跨迭代流水。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为每个 program 只会执行一次有效行迭代，没有自己的下一行工作可与当前行重叠。
+• [T#B#按行号推导]：program p 的第一次行号是 p，属于有效范围；下一次行号是 p+M，已经不小于 M，因此循环立即结束。
+• [T#B#流水所需条件]：tl.range 的跨迭代流水需要同一 program 内有多次迭代。这里只存在一行迭代，无法把下一行的工作提前放入流水。
+[T#B,!c47f17#边界]：不同 programs 仍可能被 GPU 交错调度，但这属于硬件对不同工作的调度，不能当作该 program 行循环内部的跨迭代流水。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -205,14 +214,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">occupancy 降低时，流水为什么仍可能更快？</t>
+          <t xml:space="preserve">同一个 persistent GPU kernel 保持行分配算法不变。增加软件流水深度后，即使每个 SM 的驻留数量和 occupancy 降低，执行时间为什么仍有可能缩短？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：更多独立迭代在途，可能增加指令级并行与延迟隐藏机会，抵消较少驻留 programs 的代价。
-• [T#B#因果]：当前迭代等待数据时，其他迭代的独立工作可能推进，从而减少空等。
-[T#B,!c47f17#边界]：这是可能机制；不是把单行切成更多块，也不能保证增加 stages 就会加速。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：流水可能让同一 program 中更多独立迭代的工作重叠，提高指令级并行与延迟隐藏能力；这部分收益有时可以抵消较少驻留工作的代价。
+• [T#B#怎样隐藏延迟]：当某一行迭代等待加载结果时，另一行迭代中不依赖该结果的指令可能继续推进，减少 program 只有等待而没有可做工作的时间。
+• [T#B#为何不矛盾]：occupancy 是相应测量口径下驻留 warp 数占硬件上限的比例，跨迭代并行则描述已驻留工作内部有多少独立指令可推进。驻留比例降低时，剩余工作的推进效率仍可能改善。
+[T#B,!c47f17#边界]：这是一种需要测量核验的可能机制。stages 不会自动把一行切成更多块，也不保证每次增加流水深度都会提速。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -229,14 +239,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">推导默认 grid，应使用哪份资源记录？</t>
+          <t xml:space="preserve">persistent softmax 的 wrapper 会根据每个 program 的寄存器和共享内存用量，估算驻留数量并选择默认 grid。应从哪个编译版本获取资源记录，才能让这个 grid 对应真实执行？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：使用实际 launch 所用的同一 kernel 特化的资源记录。
-• [T#B#核对]：把 kernel、shape 与编译和 launch 配置一一对应；不能套用另一特化的官方数值。
-[T#B,!c47f17#边界]：shape 或配置改变后需重新核对，不能把另一实现或另一特化的资源结果直接照搬。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：资源探测必须针对实际将被 launch 的同一 kernel 编译特化，不能用另一个实现或另一套配置的数据代替。
+• [T#B#什么叫同一特化]：需要把 kernel 实现、输入形状对应的块配置，以及 num_warps、num_stages 等编译和启动配置一一对应；这些设置可能改变编译后的资源用量。
+• [T#B#为何影响 grid]：默认 grid 由资源推导驻留能力。如果资源记录来自旧配置，后面的容量估算和 program 数就可能与真正执行的版本不匹配。
+• [T#B#排查方法]：核对资源探测与最终 launch 使用的参数是否一致。形状或配置改变后，重新确认资源记录，而不是沿用另一教程或另一实现中的固定数值。
+[T#B,!c47f17#边界]：某一特化测得的 grid 不是整个算法的常量；旧分支测试通过，也不能替代当前默认路径的验证。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -253,14 +265,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">小 M 截断了 grid，会降低资源理论 occupancy 吗？</t>
+          <t xml:space="preserve">persistent softmax 先按 GPU 资源估算可启动的 program 数，又因只有 M 行输入而把全设备 grid 限制为不超过 M。这个工作量截断会不会降低该编译特化的“资源理论 occupancy”？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会因此改写该特化按每 SM 资源推导的理论上限。
-• [T#B#区分]：实际 launch 的 program 数是工作量限制；理论上限是资源容量推导；achieved occupancy 是运行时观测。
-[T#B,!c47f17#边界]：小工作量可能无法充分使用设备，但不能把全设备 grid 直接代入每 SM 的理论上限。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不会改写它按每个 SM 资源容量推导的理论驻留上限；但实际工作量可能太少，无法让设备达到这个上限。
+• [T#B#理论上限]：资源理论 occupancy 回答“如果有足够多的工作，该特化最多能占用多少 warp 驻留容量”，依据是每份工作的资源需求和每个 SM 的资源容量。
+• [T#B#实际启动量]：grid 回答“这次在整个设备上总共启动多少个 program”。小 M 限制的是这次有多少工作，而不是每个 SM 理论上装得下多少工作。
+• [T#B#运行时观测]：achieved occupancy 是执行时实际观测到的驻留情况，会受工作量、调度及执行过程影响，需要与静态理论估算分开。
+[T#B,!c47f17#边界]：不能把被 M 截断后的全设备 grid 直接代入每个 SM 的资源容量公式，否则会把启动规模和理论驻留能力混为一谈。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -277,14 +291,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">准备后 wrapper benchmark 的计时边界是什么？</t>
+          <t xml:space="preserve">比较多种 softmax 实现时，实验目标是测量“完成一次性准备后的 Python wrapper 调用”，而不是只测 kernel。JIT 编译、资源/grid 初始化，以及每次调用的分配和检查，应分别放在什么计时边界？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：把每个 case 的 JIT、资源探测和 grid 初始化放到计时外，计时内继续调用 wrapper。
-• [T#B#保留]：每次调用的内存分配与参数检查仍计入时间。
-[T#B,!c47f17#边界]：必须用同一边界比较 providers；该结果不同于 kernel-only 或未缓存默认 API 调用。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个测试用例的一次性 JIT、资源探测和默认 grid 初始化放在计时外；计时内继续调用 wrapper，保留它每次调用需要完成的分配、参数检查与启动流程。
+• [T#B#为什么先准备]：如果每次重复资源探测，就会把初始化策略的成本带入结果；该结果不能直接代表已经准备好的常规调用。
+• [T#B#为什么仍用 wrapper]：当前实验关心使用这个接口的调用成本，因此不能为了缩小数字就改成直接 kernel launch，从而悄悄换掉被比较的对象。
+• [T#B#比较的一致性]：各个被比较实现都应采用明确且一致的准备和调用边界，并交代计时工具的测量口径。
+[T#B,!c47f17#边界]：准备后 wrapper、kernel-only，以及未缓存初始化的首次或默认 API 调用，回答的是不同问题；这些耗时不能不加说明地混用。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -301,14 +317,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">benchmark 不验正确性，验证证据从哪里来？</t>
+          <t xml:space="preserve">为了单独测量 softmax 性能，我们决定 benchmark 中只做准备、同步和计时，不执行 reference 对照。这样安排后，应由哪里保证被计时 kernel 的正确性？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：由独立功能测试提供 reference 对照等正确性证据；benchmark 负责准备、同步和计时。
-• [T#B#覆盖]：功能测试应覆盖所比较的 shape 与配置，使被计时实现有对应正确性证据。
-[T#B,!c47f17#边界]：只把检查移出 benchmark，不代表可以省略检查；性能结果本身不能证明正确。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：由独立的功能测试提供正确性证据，benchmark 本身只负责性能测量；把检查移出计时流程，不等于省略检查。
+• [T#B#需要什么检查]：功能测试把 kernel 输出与可靠 reference 对照，并按问题需要检查输出形状和数值不变量。性能数字不能说明每个输出值都算对了。
+• [T#B#怎样对应测试范围]：测试要覆盖正在比较的输入形状和配置，包括不同 stages 等实际使用的路径；只测过另一配置，不能自动证明当前被计时版本正确。
+[T#B,!c47f17#边界]：可以分开保存功能测试结果与性能结果，但报告时必须能把二者对应起来。仅证明 kernel 能运行结束，并不构成数值正确性证据。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -325,14 +342,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stages 与默认 grid 同时变化，测到的是谁的效果？</t>
+          <t xml:space="preserve">一次 persistent softmax 性能实验分别测试不同 num_stages，但每个配置又按各自编译资源选择了不同的默认 grid。测得的速度差异能否直接称为“单独增加流水深度的效果”？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：测到的是 stages、编译资源与默认 grid 共同变化后的策略效果。
-• [T#B#归因]：要研究流水深度的独立影响，需要共同显式 grid 等控制变量，并另用测量核验候选机制。
-[T#B,!c47f17#边界]：不能仅凭变慢就归因为 occupancy 降低；资源表、循环次数与时间观测必须对应当前特化。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。当前比较的是流水设置、编译资源占用和默认启动规模一起变化后的整套策略，不能把速度差异只归因于流水深度。
+• [T#B#有哪些联动]：num_stages 可能改变资源使用，资源变化又影响默认 grid；grid 改变后，每个 program 分到的行数和循环迭代数也可能改变。
+• [T#B#怎样追加对照]：若要缩小到流水深度的影响，可保持输入和实现一致，显式使用共同的 grid，再比较不同 stages；同时核对实际编译资源与计时结果。
+[T#B,!c47f17#边界]：固定 grid 只是控制一项混杂因素。要进一步断言是 occupancy、流水开销或其他机制导致变快或变慢，仍需要对应测量证据。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -349,16 +367,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">log-softmax 为什么不先算 softmax 再取 log？</t>
+          <t xml:space="preserve">对一行有限输入 x，需要计算每个位置的 log-softmax。为什么“先计算 softmax 概率，再对概率取 log”可能丢失有限结果，而直接计算稳定的 log-softmax 可以避免这个问题？</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先算概率可能下溢为 0；随后取 log 会得到负无穷，丢失原本有限的对数值。
-• [T#B#稳定路径]：令 m 为行最大值，直接减去稳定的 log-sum-exp，避免先形成很小的最终概率。
-[E##\log\operatorname{softmax}(x_i)=(x_i-m)-\log\sum_j e^{x_j-m},\quad m=\max_j x_j]
-• [T#B#最小例子]：对 \[0,-1000\]，第二项概率可能下溢；稳定 log-softmax 的第二项仍约为 -1000。
-[T#B,!c47f17#边界]：这里讨论非空、有限输入行；非有限输入需要另外约定与核验。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：很小的 softmax 概率在浮点数中可能先下溢成 0，随后取 log 就得到负无穷。直接使用稳定的对数表达式，可以避免先形成这个已经丢失精度的最终概率。
+• [T#B#定义所用量]：令 x_i 为当前元素，m 为整行的最大值，j 遍历行内所有有效元素。先减去 m，再计算指数和的对数，最后从 x_i−m 中减去它。
+[E##\log\operatorname{softmax}(x_i)=(x_i-m)-\log\sum_j e^{x_j-m},\qquad m=\max_j x_j]
+• [T#B#最小例子]：输入 \[0, -1000\] 时，第二项概率可能在浮点表示中成为 0；再取 log 只能得到负无穷。稳定公式保留原始分数 -1000，得到的第二项仍约为 -1000。
+[T#B,!c47f17#边界]：这里假设行非空且输入有限。数学上等价的表达式不保证在浮点中同样稳定；非有限输入还需要单独约定和验证。</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-02-fused-softmax-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-02-fused-softmax-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,14 +36,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 按行计算 softmax 时，通常把一行的有效列补到较大的块宽度。假设有效输入非空且全部有限，为什么 tl.load 对超出有效列数的位置应填负无穷，而不能随意填零？</t>
+          <t xml:space="preserve">Triton 按行计算 softmax 时，一个 program 用 BLOCK_SIZE = next_power_of_2(N) 的静态块装下一行，超出有效列数 N 的位置是 padding。假设有效输入非空且全部有限，为什么 tl.load 对这些 padding 位置应填负无穷，而不能随意填零？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：负无穷不会改变有效元素的最大值，并且在减去行最大值、取指数后变成 0，从而既不影响 max，也不增加 softmax 的归一化分母。
 • [T#B#先求最大值]：令 m 为有效输入的行最大值。额外的负无穷位置不会超过任何有限有效值，因此整块求 max 仍得到 m；若填零，在有效值全为负数时就会改变最大值。
-• [T#B#再取指数求和]：padding 的负无穷减去有限 m 后仍为负无穷，取 exp 得 0。把它们加入指数和，对分母没有贡献；零填充则可能产生额外正贡献。
+• [T#B#再取指数求和]：padding 的负无穷减去有限 m 后仍为负无穷，取 exp 得 0，加入指数和对分母没有贡献；填零则每个 padding 位置都会给分母加上一个正数 exp(0 − 行最大值)，必然改变归一化结果（除非该项下溢为 0）。
 • [T#B#最终输出]：只有有效列的位置需要写回；padding 只是为块级计算补齐形状，不是 softmax 输入中新增的有效元素。
 [T#B,!c47f17#边界]：上述推导要求有至少一个有效元素且有效输入有限。整行均为负无穷等情形可能遇到未定义运算，需要另行规定语义。</t>
         </is>
@@ -62,65 +62,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本课的 softmax 接口接收形状 \[M, N\] 的矩阵，其中 M 是行数，N 是每行参与 softmax 的列数。为什么约定 M=0 且 N&gt;0 可返回空结果，而 N=0 要拒绝？</t>
+          <t xml:space="preserve">数值稳定的 softmax 先求每行的最大值 m，再计算 exp(x_j − m) / Σ_k exp(x_k − m)。为什么减去 m 不改变 softmax 的结果，又能防止什么数值问题？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：没有输入行，与有一个空的行内归约维度，是两种接口情况。本练习允许前者，明确拒绝后者。
-• [T#B#没有行]：M=0 且 N&gt;0 表示没有需要处理的样本行，可以返回相同形状的空结果，不必执行任何行的 max 或 sum。
-• [T#B#没有列]：N=0 表示每行没有参与 softmax 的元素，行最大值与归一化分母没有本练习所要求的有效计算域，因此 wrapper 直接拒绝该输入。
-[T#B,!c47f17#边界]：这是 Triton Lesson 02 学习实现的接口约定；不能据此断言所有深度学习框架都会以同样方式处理空形状。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：分子和分母都乘上了同一个因子 exp(−m)，约掉后就是原式，所以结果不变；减去 m 后所有指数输入都不大于 0，exp 的结果都不超过 1，普通的有限大数就不会让 exp 上溢。
+[E##\frac{e^{x_j-m}}{\sum_k e^{x_k-m}}=\frac{e^{-m}\,e^{x_j}}{e^{-m}\sum_k e^{x_k}}=\frac{e^{x_j}}{\sum_k e^{x_k}}]
+• [T#B#为什么能防上溢]：直接计算时，较大的有限输入可能让 exp(x_j) 先上溢成 inf；减去 m 后，最大元素处 x − m = 0、exp 为 1，所以分母至少为 1，其余各项都不超过 1。
+[T#B,!c47f17#边界]：它只防住有限大数的上溢，不保证所有特殊值都有限：含 +inf 时 +inf − (+inf) 得 NaN；一行没有有效元素、只剩 −inf padding 时，−inf − (−inf) 也是 NaN，这类输入要由接口约定处理。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">没有行 ≠ 行内归约域为空</t>
+          <t xml:space="preserve">同乘 exp(−m) → 比值不变；指数输入 ≤ 0 → 不上溢</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · B #005–009、#019–024 · 接口纠错</t>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · A #007 · 数值稳定</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">测试按行计算的 softmax kernel 时，假设每行非空且有效输入都为有限值，我们希望检查“每行元素之和接近 1”这一不变量。应该对输入矩阵 X 还是输出矩阵 Y 求行和，为什么？</t>
+          <t xml:space="preserve">对 M×N 矩阵按行做 softmax。naive 的 PyTorch 写法分五步：row max → subtract → exp → row sum → divide，每一步都把结果写回全局内存，下一步再读出来。分别估算它和一个 fused kernel 的全局内存搬运量（以元素计），并说明 fusion 省下的是什么。</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：应检查输出 Y 的每行之和接近 1。softmax 把一行输入变成归一化权重，约束属于归一化后的输出，而不属于原始输入。
-• [T#B#输入没有此约束]：输入可以是任意有限分数。例如输入行 \[2, 3\] 的和为 5，并不影响它成为合法的 softmax 输入。
-• [T#B#输出为何归一化]：每个输出都是该位置的指数值除以整行指数和。将所有输出相加，分子合起来就是同一个分母，所以数学上的结果为 1。
-[T#B,!c47f17#边界]：浮点结果按合理容差比较。仅通过行和检查仍不足以证明每个输出正确，还应与可靠 reference 逐元素对照。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：naive 约搬运 8MN + 4M 个元素，fused 理想情况下只读一次输入、写一次输出，共 2MN 个元素，大矩阵时流量比接近 4 倍；fusion 省下的是中间结果在全局内存上的往返，不是 max、exp、sum、divide 这些计算。
+• [T#B#逐步计数]：row max 读 MN、写 M；subtract 读 MN + M、写 MN；exp 读 MN、写 MN；row sum 读 MN、写 M；divide 读 MN + M、写 MN。合计读 5MN + 2M、写 3MN + 2M。
+[E##\frac{8MN+4M}{2MN}=4+\frac{2}{N}]
+• [T#B#fused 为何只要 2MN]：fused kernel 把一行读进来后，减最大值、exp、求和与除法的中间结果都不再写回全局内存，最后只写一次输出。
+[T#B,!c47f17#边界]：约 4 倍是理论流量比，不是运行时间的保证：本机实测 fused 的 Triton 明显快于 naive，但并非在每个列宽上都快于 torch.softmax。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">归一化约束属于输出</t>
+          <t xml:space="preserve">5 读 3 写 → 1 读 1 写：约 4×，省的是 DRAM 往返</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · B #013–016 · 行和纠错</t>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · A #007、D #006 · fusion 流量</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton persistent softmax 中，一个 program 会在行循环里依次处理多行。该循环 tl.range(..., num_stages=s) 的 num_stages 描述什么流水范围，能把 s 理解成 s 个独立 worker 吗？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的 persistent softmax 中，一个 program 用 for row in tl.range(start, M, step, num_stages=s) 依次处理多行。这里的 num_stages 描述的是什么范围内的流水？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。这里 num_stages 为同一个 program 内不同循环迭代的在途与重叠提供机会，实际如何调度由编译器决定。
-• [T#B#迭代是什么]：一次迭代计算一行 softmax。存在多次迭代时，编译器可以尝试让不同迭代中可独立推进的工作重叠。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它描述同一个 program 内行循环的跨迭代流水：不同行的迭代可以同时在途、相互重叠，具体怎样重叠由编译器安排。
+• [T#B#迭代是什么]：一次迭代计算一行 softmax；只有同一个 program 有多次迭代时，后一行的工作才可能与前一行重叠。
 • [T#B#依赖仍存在]：对于同一行，加载后才能求最大值，再计算指数、指数和、归一化和写回。这些依赖不会因为 num_stages 变大而消失。
-[T#B,!c47f17#边界]：stage 不是独立 program 或 worker，也不表示把一行机械切成 s 段并行处理；这里讨论的特定作用域是行循环的跨迭代流水。</t>
+[T#B,!c47f17#边界]：stage 不是独立的 program 或 worker，也不表示把一行机械切成 s 段并行处理。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -137,36 +138,10 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">对同一个 GPU kernel，增加软件流水深度后，若编译结果显示每个 program 使用更多寄存器或共享内存，这种资源变化为什么可能减少每个 SM 的并行驻留数量？</t>
+          <t xml:space="preserve">persistent softmax 有 M 行输入，启动 P 个 program（P&gt;0）。编号 p 的 program 从行 p 开始，每次增加 P，直到行号达到 M。怎样证明这种 grid-stride 分配让每一行恰好被处理一次？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 SM 的资源总量有限；一个 program 占用更多受限资源时，SM 能同时容纳的 program 数可能减少。
-• [T#B#驻留的含义]：驻留是 program 的执行状态与资源已经放在该 SM 上，能够等待或参与调度；它描述的是同时容纳多少份工作。
-• [T#B#容量如何受限]：可以把每个 program 需要的寄存器、共享内存等分别与 SM 的容量比较；其中最紧的约束会限制可同时驻留的数量。
-• [T#B#不能直接推出什么]：并行驻留数降低，并不等价于某一次 stage 本身执行更慢。若要说单个 program 因 spilling 等原因变慢，还需要该机制的证据。
-[T#B,!c47f17#边界]：增加 stages 不保证寄存器和共享内存都增长，也不保证正好保存同样数量的完整行；应检查实际编译特化的资源记录。</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单份资源 ↑ → 同时驻留可能 ↓</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · A #013–016、C #006–009 · 资源代价</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">persistent softmax 有 M 行输入，启动 P 个 program（P&gt;0）。编号 p 的 program 从行 p 开始，每次增加 P，直到行号达到 M。怎样证明这种 grid-stride 分配让每一行恰好被处理一次？</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：对任意合法行号，除以 P 得到唯一的商和余数；余数确定负责它的 program，商确定该 program 的循环迭代，所以既不会漏行，也不会重行。
 • [T#B#符号定义]：设 r 是行号，满足 0≤r&lt;M；p 是 program 编号，满足 0≤p&lt;P；k 是从 0 开始的迭代编号。它们满足以下对应关系。
@@ -175,49 +150,24 @@
 [T#B,!c47f17#边界]：循环必须以 r&lt;M 为条件，并使用同一个正步长 P。证明依赖这套静态行分配规则，而不是仅凭某个数字例子看起来覆盖完整。</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">商余数唯一 → 行归属唯一</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #006–013 · 覆盖证明转折</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">persistent softmax 共有 M 行，program p 依次处理 p、p+P、p+2P 等行，其中 P 是启动的 program 数。如果实际启动 P=M，为什么增加行循环的 num_stages 不能产生同一 program 的跨行流水？</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：因为每个 program 只会执行一次有效行迭代，没有自己的下一行工作可与当前行重叠。
-• [T#B#按行号推导]：program p 的第一次行号是 p，属于有效范围；下一次行号是 p+M，已经不小于 M，因此循环立即结束。
-• [T#B#流水所需条件]：tl.range 的跨迭代流水需要同一 program 内有多次迭代。这里只存在一行迭代，无法把下一行的工作提前放入流水。
-[T#B,!c47f17#边界]：不同 programs 仍可能被 GPU 交错调度，但这属于硬件对不同工作的调度，不能当作该 program 行循环内部的跨迭代流水。</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每 program 一行 → 无下一迭代</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #006–013 · 作用域纠错</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同一个 persistent GPU kernel 保持行分配算法不变。增加软件流水深度后，即使每个 SM 的驻留数量和 occupancy 降低，执行时间为什么仍有可能缩短？</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一个 persistent GPU kernel 保持行分配算法不变。增大 tl.range 行循环的 num_stages（软件流水深度）后，即使每个 SM 的驻留数量和 occupancy 降低，执行时间为什么仍有可能缩短？</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：流水可能让同一 program 中更多独立迭代的工作重叠，提高指令级并行与延迟隐藏能力；这部分收益有时可以抵消较少驻留工作的代价。
 • [T#B#怎样隐藏延迟]：当某一行迭代等待加载结果时，另一行迭代中不依赖该结果的指令可能继续推进，减少 program 只有等待而没有可做工作的时间。
@@ -225,152 +175,152 @@
 [T#B,!c47f17#边界]：这是一种需要测量核验的可能机制。stages 不会自动把一行切成更多块，也不保证每次增加流水深度都会提速。</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">跨迭代独立工作 → 延迟隐藏机会</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #006–014 · 指令级并行纠错</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">persistent softmax 的 wrapper 先按每个 program 的寄存器和共享内存用量估算每个 SM 能驻留几个 program，再据此（并以行数 M 为上限）选择默认 grid。复算官方教程 kernel（num_stages=4）的资源时得到 grid 648。你自己写的简化 persistent kernel，应该用什么来确定默认 grid？</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：用它自己实际要 launch 的那份编译特化的资源记录；官方特化算出的 648 只属于那份特化，不能拿来代替。
+• [T#B#什么叫同一特化]：需要把 kernel 实现、输入形状对应的块配置，以及 num_warps、num_stages 等编译和启动配置一一对应；这些设置可能改变编译后的资源用量。
+• [T#B#为何影响 grid]：默认 grid 由资源推导驻留能力。如果资源记录来自旧配置，后面的容量估算和 program 数就可能与真正执行的版本不匹配。
+• [T#B#反例]：学习中写的简化 kernel 在 N=781 下实际读取资源后，stages 1/2/4 的默认 grid 都是 864，而不是官方特化的 648。
+• [T#B#排查方法]：核对资源探测与最终 launch 的参数是否一致，例如块大小要按列数 N 取 next_power_of_2(N)；形状或配置改变后重新读取资源。
+[T#B,!c47f17#边界]：某一特化测得的 grid 不是整个算法的常量；旧分支测试通过，也不能替代当前默认路径的验证。</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">实际 launch 特化 = 资源探测特化</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #039–044、#129–130、#135–137、#146 · 默认 grid 复审</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">persistent softmax 先按每个 SM 的资源容量推导该特化的理论驻留上限，再因为只有 M 行，把全设备 grid 限制为不超过 M。M 很小、实际只 launch 1 个 program 时，这个特化的资源理论 occupancy 应该怎样计算？</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：仍按该特化单个 program 的资源需求与每个 SM 的资源容量推导，结果不受 M 截断影响；截断只减少这次实际启动的 program 数，设备因此达不到这个上限。
+• [T#B#理论上限]：资源理论 occupancy 回答“如果有足够多的工作，该特化最多能占用多少 warp 驻留容量”，依据是每份工作的资源需求和每个 SM 的资源容量。
+• [T#B#实际启动量]：grid 回答“这次在整个设备上总共启动多少个 program”。小 M 限制的是这次有多少工作，而不是每个 SM 理论上装得下多少工作。
+• [T#B#延伸]：achieved occupancy 是执行时实际观测到的驻留情况，会受工作量、调度及执行过程影响，需要与静态理论估算分开。
+[T#B,!c47f17#边界]：不能把被 M 截断后的全设备 grid 直接代入每个 SM 的资源容量公式，否则会把启动规模和理论驻留能力混为一谈。</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">跨迭代独立工作 → 延迟隐藏机会</t>
+          <t xml:space="preserve">资源容量 · launch 数 · 运行时观测</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #006–014 · 指令级并行纠错</t>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #112–113、#137 · occupancy 公式复审</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">persistent softmax 的 wrapper 会根据每个 program 的寄存器和共享内存用量，估算驻留数量并选择默认 grid。应从哪个编译版本获取资源记录，才能让这个 grid 对应真实执行？</t>
+          <t xml:space="preserve">比较 persistent softmax 与 torch.softmax 等实现的速度时，有人主张“只有预分配输出、直接 launch kernel 才公平”。若实验要回答的是各实现作为 Python 接口被调用时的成本，计时边界应怎样划？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：资源探测必须针对实际将被 launch 的同一 kernel 编译特化，不能用另一个实现或另一套配置的数据代替。
-• [T#B#什么叫同一特化]：需要把 kernel 实现、输入形状对应的块配置，以及 num_warps、num_stages 等编译和启动配置一一对应；这些设置可能改变编译后的资源用量。
-• [T#B#为何影响 grid]：默认 grid 由资源推导驻留能力。如果资源记录来自旧配置，后面的容量估算和 program 数就可能与真正执行的版本不匹配。
-• [T#B#排查方法]：核对资源探测与最终 launch 使用的参数是否一致。形状或配置改变后，重新确认资源记录，而不是沿用另一教程或另一实现中的固定数值。
-[T#B,!c47f17#边界]：某一特化测得的 grid 不是整个算法的常量；旧分支测试通过，也不能替代当前默认路径的验证。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：计时边界由要回答的问题决定：一次性的 JIT、资源探测和默认 grid 初始化放在计时外；计时内继续调用 wrapper，保留每次调用都要做的分配、参数检查与 launch，各实现在同一 API 层级比较。
+• [T#B#为什么先准备]：如果每次重复资源探测，就会把初始化策略的成本带入结果；该结果不能直接代表已经准备好的常规调用。
+• [T#B#为何不改测 kernel-only]：其他实现的调用同样包含分配和检查；只把自己的实现改成直接 launch kernel，会悄悄换掉被比较的对象。
+[T#B,!c47f17#边界]：准备后 wrapper、kernel-only，以及未缓存初始化的首次或默认 API 调用，回答的是不同问题；这些耗时不能不加说明地混用。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">实际 launch 特化 = 资源探测特化</t>
+          <t xml:space="preserve">一次性准备在外 · 每次 wrapper 成本在内</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #039–044、#129–130、#146 · 默认 grid 复审</t>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #113–122 · benchmark 口径转折</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">persistent softmax 先按 GPU 资源估算可启动的 program 数，又因只有 M 行输入而把全设备 grid 限制为不超过 M。这个工作量截断会不会降低该编译特化的“资源理论 occupancy”？</t>
+          <t xml:space="preserve">Triton fused softmax 中，每个 program 用 BLOCK_SIZE = triton.next_power_of_2(N) 的静态块装下一整行，再在块内做 max 与 sum。为什么块要这样确定，这种“一行一块”的设计又有什么代价和上限？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会改写它按每个 SM 资源容量推导的理论驻留上限；但实际工作量可能太少，无法让设备达到这个上限。
-• [T#B#理论上限]：资源理论 occupancy 回答“如果有足够多的工作，该特化最多能占用多少 warp 驻留容量”，依据是每份工作的资源需求和每个 SM 的资源容量。
-• [T#B#实际启动量]：grid 回答“这次在整个设备上总共启动多少个 program”。小 M 限制的是这次有多少工作，而不是每个 SM 理论上装得下多少工作。
-• [T#B#运行时观测]：achieved occupancy 是执行时实际观测到的驻留情况，会受工作量、调度及执行过程影响，需要与静态理论估算分开。
-[T#B,!c47f17#边界]：不能把被 M 截断后的全设备 grid 直接代入每个 SM 的资源容量公式，否则会把启动规模和理论驻留能力混为一谈。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Triton 的归约需要编译期已知的块形状，而 max 与 sum 都要覆盖整行，所以块必须一次装下整行，取不小于 N 的最小 2 的幂；代价是块随 N 跳档、每档都是另一份编译特化，而且整行 padding 后必须装进片上资源，太长的行不能直接沿用。
+• [T#B#静态块]：例如 N=781 时 BLOCK_SIZE=1024：781 个有效 lane、243 个 padding lane；padding 只是 program 内部的逻辑位置，用 −∞ 填充，不会写回。
+• [T#B#越过 2 的幂]：N 只多一列，块就可能翻倍：N=32 时块为 32，N=33 时实际特化的块是 64。块变了就是另一份编译特化，寄存器、共享内存、驻留数和默认 grid 都要按新特化重新读取，不能沿用旧 N 的资源表。
+[T#B,!c47f17#边界]：一整行 padding 后必须能装进单个 program 可用的片上资源；教程实现没有处理超大列宽，N 很大时不能只靠继续调大 BLOCK_SIZE 沿用这个设计。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">资源容量 · launch 数 · 运行时观测</t>
+          <t xml:space="preserve">编译期块形状 + 整行归约 → next_power_of_2；越档即换特化；须装进片上</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #112–113、#137 · occupancy 公式复审</t>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · A #007、C #135–137、D #003–006 · 整行静态块</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">比较多种 softmax 实现时，实验目标是测量“完成一次性准备后的 Python wrapper 调用”，而不是只测 kernel。JIT 编译、资源/grid 初始化，以及每次调用的分配和检查，应分别放在什么计时边界？</t>
+          <t xml:space="preserve">一次 persistent softmax 实验比较 num_stages=1/2/4，但每个配置都按各自的编译资源推导默认 grid，例如 N=2049 时三个 stage 的 grid 分别是 432、540、324。这组速度差异比较的究竟是什么？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个测试用例的一次性 JIT、资源探测和默认 grid 初始化放在计时外；计时内继续调用 wrapper，保留它每次调用需要完成的分配、参数检查与启动流程。
-• [T#B#为什么先准备]：如果每次重复资源探测，就会把初始化策略的成本带入结果；该结果不能直接代表已经准备好的常规调用。
-• [T#B#为什么仍用 wrapper]：当前实验关心使用这个接口的调用成本，因此不能为了缩小数字就改成直接 kernel launch，从而悄悄换掉被比较的对象。
-• [T#B#比较的一致性]：各个被比较实现都应采用明确且一致的准备和调用边界，并交代计时工具的测量口径。
-[T#B,!c47f17#边界]：准备后 wrapper、kernel-only，以及未缓存初始化的首次或默认 API 调用，回答的是不同问题；这些耗时不能不加说明地混用。</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一次性准备在外 · 每次 wrapper 成本在内</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #113–122 · benchmark 口径转折</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">为了单独测量 softmax 性能，我们决定 benchmark 中只做准备、同步和计时，不执行 reference 对照。这样安排后，应由哪里保证被计时 kernel 的正确性？</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：由独立的功能测试提供正确性证据，benchmark 本身只负责性能测量；把检查移出计时流程，不等于省略检查。
-• [T#B#需要什么检查]：功能测试把 kernel 输出与可靠 reference 对照，并按问题需要检查输出形状和数值不变量。性能数字不能说明每个输出值都算对了。
-• [T#B#怎样对应测试范围]：测试要覆盖正在比较的输入形状和配置，包括不同 stages 等实际使用的路径；只测过另一配置，不能自动证明当前被计时版本正确。
-[T#B,!c47f17#边界]：可以分开保存功能测试结果与性能结果，但报告时必须能把二者对应起来。仅证明 kernel 能运行结束，并不构成数值正确性证据。</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">功能测试证正确 · benchmark 测性能</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · C #148–152 · 验证职责调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一次 persistent softmax 性能实验分别测试不同 num_stages，但每个配置又按各自编译资源选择了不同的默认 grid。测得的速度差异能否直接称为“单独增加流水深度的效果”？</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。当前比较的是流水设置、编译资源占用和默认启动规模一起变化后的整套策略，不能把速度差异只归因于流水深度。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：比较的是流水设置、编译资源占用和默认启动规模一起变化后的整套默认策略，不能把速度差异只归因于流水深度。
 • [T#B#有哪些联动]：num_stages 可能改变资源使用，资源变化又影响默认 grid；grid 改变后，每个 program 分到的行数和循环迭代数也可能改变。
 • [T#B#怎样追加对照]：若要缩小到流水深度的影响，可保持输入和实现一致，显式使用共同的 grid，再比较不同 stages；同时核对实际编译资源与计时结果。
 [T#B,!c47f17#边界]：固定 grid 只是控制一项混杂因素。要进一步断言是 occupancy、流水开销或其他机制导致变快或变慢，仍需要对应测量证据。</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">联动策略比较 ≠ stage 单因素因果</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · D #001–006 · 结论范围收紧</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">对一行有限输入 x，需要计算每个位置的 log-softmax。为什么“先计算 softmax 概率，再对概率取 log”可能丢失有限结果，而直接计算稳定的 log-softmax 可以避免这个问题？</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：很小的 softmax 概率在浮点数中可能先下溢成 0，随后取 log 就得到负无穷。直接使用稳定的对数表达式，可以避免先形成这个已经丢失精度的最终概率。
 • [T#B#定义所用量]：令 x_i 为当前元素，m 为整行的最大值，j 遍历行内所有有效元素。先减去 m，再计算指数和的对数，最后从 x_i−m 中减去它。
@@ -379,14 +329,39 @@
 [T#B,!c47f17#边界]：这里假设行非空且输入有限。数学上等价的表达式不保证在浮点中同样稳定；非有限输入还需要单独约定和验证。</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">保留对数域 → 避免概率先下溢</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · E #001–004 · log-softmax 快速回顾</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUDA 中常见的 persistent kernel 会在 while 循环里不断从任务队列取任务；Triton fused softmax 的 persistent 版本则让每个 program 用有界的 for 依次处理 pid、pid+P、pid+2P… 行。两种做法的任务分配方式差在哪里，各适合什么样的任务？</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：差在任务何时分配：softmax 的行在 launch 前全部已知、每行工作量相同，可以按公式静态分给各 program；动态队列在运行时让先空闲的 program 继续取任务，适合数量多、耗时差异很大的任务。判断依据是任务来源与成本差异，而不是循环写成 for 还是 while。
+• [T#B#静态分配]：program p 由自己的编号直接算出负责的行，不需要运行时取任务或互相协调。
+• [T#B#动态分配]：任务耗时差异很大时，静态分配可能让一些 program 早早做完、另一些还压着重任务；动态取任务让完成得早的 program 接着处理剩下的任务。
+[T#B,!c47f17#边界]：Triton softmax 的有界 for 同样属于 persistent 写法，只是任务在 launch 前就已分好。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">launch 前已知且等成本 → 静态公式；耗时差异大 → 运行时取任务</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fused Softmax 学习日志 · 2026-08-07 · A #013–018 · persistent 两种形态</t>
         </is>
       </c>
     </row>
